--- a/hardware/pcb_files/brick/14-09-26_brick_BOM_total.xlsx
+++ b/hardware/pcb_files/brick/14-09-26_brick_BOM_total.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8ea81d3991f4556b/Bachelorarbeit/Förderschule/Technik/cubes_platformIO/hardware/pcb_files/brick/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{666569E2-A539-4A76-8ABE-ED6E34CC5ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE09EF8F-1397-4531-9287-1EC13AF64523}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{666569E2-A539-4A76-8ABE-ED6E34CC5ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3855A237-1CBF-42C8-82A0-7ED7FEFBA939}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{26D3D36A-241F-4D36-8B58-3CF6904C552A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{26D3D36A-241F-4D36-8B58-3CF6904C552A}"/>
   </bookViews>
   <sheets>
     <sheet name="brick_kicad" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="81">
   <si>
     <t>Reference</t>
   </si>
@@ -407,10 +407,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -779,20 +775,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{464171C5-A331-4A91-98F3-B45F21F4A653}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="44.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="68.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="93.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="67.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="68.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="81.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="67.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="93.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="67.1328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="81.1328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="67.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -812,7 +808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -832,7 +828,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -852,7 +848,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -872,7 +868,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -892,7 +888,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -912,7 +908,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -932,7 +928,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -945,14 +941,14 @@
       <c r="D8" t="s">
         <v>24</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -972,7 +968,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -992,7 +988,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1012,7 +1008,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1032,7 +1028,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -1052,7 +1048,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -1072,7 +1068,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -1092,7 +1088,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -1112,7 +1108,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -1132,7 +1128,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>52</v>
       </c>
@@ -1152,7 +1148,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>56</v>
       </c>
@@ -1172,7 +1168,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>59</v>
       </c>
@@ -1192,7 +1188,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>75</v>
       </c>
@@ -1206,7 +1202,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -1226,7 +1222,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -1240,7 +1236,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>71</v>
       </c>
@@ -1254,7 +1250,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>72</v>
       </c>
@@ -1268,7 +1264,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>73</v>
       </c>
@@ -1282,7 +1278,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>74</v>
       </c>
@@ -1300,11 +1296,12 @@
     <hyperlink ref="D28" r:id="rId3" xr:uid="{23416B65-8D24-498A-9D74-545354BB1118}"/>
     <hyperlink ref="E21" r:id="rId4" xr:uid="{E0669F60-F822-4FED-8F6A-6F36C4DE1E53}"/>
     <hyperlink ref="E4" r:id="rId5" xr:uid="{0E7B9D80-258B-403B-83D0-4FAA87CF8527}"/>
+    <hyperlink ref="E8" r:id="rId6" xr:uid="{F9D291A4-CB85-466F-B367-548CB8721CF7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <tableParts count="2">
-    <tablePart r:id="rId6"/>
     <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1312,7 +1309,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A3D7B8-E5CF-4827-94C4-9D794007A8AF}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
